--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0030.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0030.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>…{PlayerName}? Vậy là ta đã quen {Male=hắn;Female=cô} từ trước rồi à?</t>
+          <t>…{PlayerName}? Vậy là tao đã quen {Male=him;Female=her} từ trước rồi à?</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Hahaha! Đúng rồi! {Male=Hắn;Female=Cô ấy} đúng là thỏi nam châm hút đủ thứ chuyện vui. Giờ thì xem chúng ta còn khuấy động được gì nào!</t>
+          <t>Hahaha! Đúng rồi! {Male=He;Female=She} đúng là thỏi nam châm hút đủ thứ chuyện vui. Giờ thì xem chúng ta còn khuấy động được gì nào!</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Ta chưa bao giờ hỏi nhiều về Bờ Biển Đen hay quá khứ của {Male=cậu ấy;Female=cô ấy}.</t>
+          <t>Ta chưa bao giờ hỏi nhiều về Bờ Biển Đen hay quá khứ của anh ấy/cô ấy.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Ở Bãi Đen này, {Male=anh ấy;Female=cô ấy} là người bị mắc kẹt nhất... cho đến giờ.</t>
+          <t>Ở Bãi Đen này, {Male=he;Female=she} là người bị mắc kẹt nhất... cho đến giờ.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Nhưng giờ đây, {PlayerName} lại muốn rời đi… thậm chí từ bỏ cả những ký ức của {Male=mình;Female=mình} sao?</t>
+          <t>Nhưng giờ đây, {PlayerName} lại muốn rời đi… thậm chí từ bỏ cả những ký ức của {Male=his;Female=her} sao?</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>...Tch. Bọn họ có ý tốt, nhưng... ta hiểu bản thân mình hơn ai hết.</t>
+          <t>...Tch. Bọn họ có ý tốt, nhưng... tao hiểu bản thân mình hơn ai hết.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>{PlayerName} đã biến mất. Ta có thể chọn chờ đợi, nhưng liệu {Male=hắn;Female:cô ấy} có thực sự trở lại?</t>
+          <t>{PlayerName} đã biến mất. Ta có thể chọn chờ đợi, nhưng liệu {Male=he;Female=she} có thực sự trở lại?</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Nếu tớ không bao giờ gặp lại {Male=anh ấy;Female=cô ấy} nữa thì sao?</t>
+          <t>Nếu tớ không bao giờ gặp lại {Male=him;Female=her} nữa thì sao?</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Nghỉ ngơi cũng chẳng ích gì… Ta đã mất đi điểm tựa rồi. {Male=Hắn;Female=Nàng} không còn ở đây để kềm chế ta nữa.</t>
+          <t>Nghỉ ngơi cũng chẳng ích gì… Ta đã mất đi điểm tựa rồi. {Male=He;Female=She} không còn ở đây để kềm chế ta nữa.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Ma Trận Stellar bắt đầu phản kháng rồi. Ta phải nhanh chóng hạ gục nó thôi.</t>
+          <t>Ma Trận Stellar bắt đầu phản kháng rồi. Tao phải nhanh chóng hạ gục nó thôi.</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Bị giam cầm trong thân xác này, phải cầu xin {Male=hắn;Female=cô ta} thương hại để có tình yêu và sự quan tâm...</t>
+          <t>Bị giam cầm trong thân xác này, phải cầu xin {Male=his;Female=her} thương hại để có tình yêu và sự quan tâm...</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Nếu kết cục là như thế, thà ta chết ngay tại chỗ còn hơn!</t>
+          <t>Nếu kết cục là như thế, thà tao chết ngay tại chỗ còn hơn!</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Ui, người ta... lại khó chịu nữa rồi... Có phải do môi trường không nhỉ?</t>
+          <t>Ui, người tao... lại khó chịu nữa rồi... Có phải do môi trường không nhỉ?</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Dù một ngày nào đó {PlayerName} có trở lại, ta sẽ làm được gì cho {Male=anh ấy;Female=cô ấy} đây?</t>
+          <t>Dù một ngày nào đó {PlayerName} có trở lại, ta sẽ làm được gì cho {Male=him;Female=her} đây?</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Mình sẽ để lại chiếc vòng tay mà {Male=anh ấy;Female=cô ấy} tặng ở Bãi Đen này.</t>
+          <t>Mình sẽ để lại chiếc vòng tay mà {Male=he;Female=she} tặng ở Bãi Đen này.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Lý trí là món quà mà {Male=anh ấy;Female=cô ấy} ban tặng. Ta sẽ không dễ dàng từ bỏ nó đâu.</t>
+          <t>Lý trí là món quà mà {Male=him;Female=her} ban tặng. Ta sẽ không dễ dàng từ bỏ nó đâu.</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Dù có hay không ký ức, bản năng vẫn sẽ dẫn ta đến bên {Male=anh ấy;Female=cô ấy}.</t>
+          <t>Dù có hay không ký ức, bản năng vẫn sẽ dẫn ta đến bên {Male=him;Female=her}.</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Khi ta gặp lại, ta mong {Male=anh ấy;Female=cô ấy} vẫn là đối thủ xứng tầm của ta. Dù là bạn hay thù, cùng nhau tự do không gò bó... Đó là giấc mơ thành hiện thực!</t>
+          <t>Khi ta gặp lại, ta mong {Male=he;Female=she} vẫn là đối thủ xứng tầm của ta. Dù là bạn hay thù, cùng nhau tự do không gò bó... Đó là giấc mơ thành hiện thực!</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Ta sẽ vứt bỏ ký ức của mình như {PlayerName} đã từng làm, phong ấn chúng đi.</t>
+          <t>Tao sẽ vứt bỏ ký ức của mình như {PlayerName} đã từng làm, phong ấn chúng đi.</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Và giờ đây? Cậu chỉ là một &lt;i&gt;kẻ thua cuộc&lt;/i&gt; mà thôi.</t>
+          <t>Và giờ đây? Mày chỉ là một &lt;i&gt;kẻ thua cuộc&lt;/i&gt; mà thôi.</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Còn cậu biết gì nào?</t>
+          <t>Còn mày biết gì nào?</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Cậu… sẽ không bao giờ sánh bằng {Male=hắn;Female=nàng}. Không bao giờ.</t>
+          <t>Cậu… sẽ không bao giờ sánh bằng {Male=his;Female=her}. Không bao giờ.</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Lúc ta gia nhập Fractsidus, chúng ta đã gặp nhau trên chiến trường.</t>
+          <t>Lúc tao gia nhập Fractsidus, chúng ta đã gặp nhau trên chiến trường.</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Tốt, các hoa văn đã sáng lên rồi. Giờ ta có thể xoay bệ này được rồi.</t>
+          <t>Tốt, các hoa văn đã sáng lên rồi. Giờ tao có thể xoay bệ này được rồi.</t>
         </is>
       </c>
     </row>
